--- a/Catch and index models/Sintese_3_modelos/tabela_cenarios_3modelos.xlsx
+++ b/Catch and index models/Sintese_3_modelos/tabela_cenarios_3modelos.xlsx
@@ -109,19 +109,19 @@
     <t>zBRT · Vieira</t>
   </si>
   <si>
+    <t>Target_switch_Santos (2018)</t>
+  </si>
+  <si>
+    <t>Mudança de alvo</t>
+  </si>
+  <si>
+    <t>Mudança de alvo · Santos</t>
+  </si>
+  <si>
     <t>Target_switch_Jardim (1999)</t>
   </si>
   <si>
-    <t>Mudança de alvo</t>
-  </si>
-  <si>
     <t>Mudança de alvo · Jardim</t>
-  </si>
-  <si>
-    <t>Target_switch_Santos (2018)</t>
-  </si>
-  <si>
-    <t>Mudança de alvo · Santos</t>
   </si>
   <si>
     <t>Target_switch_Vieira (2019)</t>
@@ -777,31 +777,31 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0.700435392853996</v>
+        <v>0.694039095473824</v>
       </c>
       <c r="F2">
-        <v>0.333651514940898</v>
+        <v>0.3449326038399905</v>
       </c>
       <c r="G2">
-        <v>1.953129275441363</v>
+        <v>1.81654552815128</v>
       </c>
       <c r="H2">
-        <v>0.1987312218050295</v>
+        <v>0.2020799680056555</v>
       </c>
       <c r="I2">
-        <v>0.07722559442411364</v>
+        <v>0.08094756698351306</v>
       </c>
       <c r="J2">
-        <v>0.417986367442244</v>
+        <v>0.4019021735320453</v>
       </c>
       <c r="K2">
-        <v>0.198235726417925</v>
+        <v>0.1942719818285945</v>
       </c>
       <c r="L2">
-        <v>1760.90889469574</v>
+        <v>1767.119449113715</v>
       </c>
       <c r="M2">
-        <v>24735.4177367644</v>
+        <v>24729.8591390633</v>
       </c>
       <c r="N2">
         <v>0.719</v>
@@ -830,28 +830,28 @@
         <v>0.714816106284109</v>
       </c>
       <c r="F3">
-        <v>0.217566300358364</v>
+        <v>0.2422341590451235</v>
       </c>
       <c r="G3">
-        <v>1.46160078816547</v>
+        <v>1.569826989874683</v>
       </c>
       <c r="H3">
-        <v>0.200965474201467</v>
+        <v>0.201633048627397</v>
       </c>
       <c r="I3">
-        <v>0.113132353138944</v>
+        <v>0.1131550647727406</v>
       </c>
       <c r="J3">
-        <v>0.65368820041514</v>
+        <v>0.5679923707847745</v>
       </c>
       <c r="K3">
-        <v>0.200834591982934</v>
+        <v>0.201330535641</v>
       </c>
       <c r="L3">
-        <v>1694.93066930839</v>
+        <v>1696.85068390468</v>
       </c>
       <c r="M3">
-        <v>24781.8892859746</v>
+        <v>24767.6939381216</v>
       </c>
       <c r="N3">
         <v>0.771</v>
@@ -877,31 +877,31 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>0.768676509701596</v>
+        <v>0.7497519345605315</v>
       </c>
       <c r="F4">
-        <v>0.219952488838889</v>
+        <v>0.2206519537416903</v>
       </c>
       <c r="G4">
-        <v>1.57381285675337</v>
+        <v>1.561704446095015</v>
       </c>
       <c r="H4">
-        <v>0.198246363808435</v>
+        <v>0.1981789252717475</v>
       </c>
       <c r="I4">
-        <v>0.1054533883360489</v>
+        <v>0.1040080921461113</v>
       </c>
       <c r="J4">
-        <v>0.669064736331233</v>
+        <v>0.6701504194769574</v>
       </c>
       <c r="K4">
         <v>0.205423424045382</v>
       </c>
       <c r="L4">
-        <v>1701.3941721473</v>
+        <v>1700.956682330075</v>
       </c>
       <c r="M4">
-        <v>24735.9826603963</v>
+        <v>24750.5047949074</v>
       </c>
       <c r="N4">
         <v>0.738</v>
@@ -927,31 +927,31 @@
         <v>26</v>
       </c>
       <c r="E5">
-        <v>1.29837432389693</v>
+        <v>1.31275252651523</v>
       </c>
       <c r="F5">
-        <v>0.5665066291094906</v>
+        <v>0.5380362794695894</v>
       </c>
       <c r="G5">
-        <v>2.34464429546194</v>
+        <v>2.360006956553401</v>
       </c>
       <c r="H5">
-        <v>0.1094099436514885</v>
+        <v>0.108910067195808</v>
       </c>
       <c r="I5">
-        <v>0.06270304024457311</v>
+        <v>0.0616301102245088</v>
       </c>
       <c r="J5">
-        <v>0.2417132616716098</v>
+        <v>0.2663002465453781</v>
       </c>
       <c r="K5">
-        <v>0.375729691040316</v>
+        <v>0.375654043152401</v>
       </c>
       <c r="L5">
-        <v>1746.45846909283</v>
+        <v>1747.04028803187</v>
       </c>
       <c r="M5">
-        <v>24627.2619866802</v>
+        <v>24561.5131914528</v>
       </c>
       <c r="N5">
         <v>0.192</v>
@@ -977,31 +977,31 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>1.34484350982725</v>
+        <v>1.33066673526375</v>
       </c>
       <c r="F6">
-        <v>0.479319853915307</v>
+        <v>0.4637326886655494</v>
       </c>
       <c r="G6">
-        <v>2.232366845145672</v>
+        <v>2.238459316111328</v>
       </c>
       <c r="H6">
-        <v>0.10747502172192</v>
+        <v>0.107173279495576</v>
       </c>
       <c r="I6">
-        <v>0.0619372890967064</v>
+        <v>0.061883641786404</v>
       </c>
       <c r="J6">
-        <v>0.282298384016867</v>
+        <v>0.296652507917467</v>
       </c>
       <c r="K6">
-        <v>0.382798867133483</v>
+        <v>0.381173347283714</v>
       </c>
       <c r="L6">
-        <v>1759.52675373347</v>
+        <v>1759.62024436513</v>
       </c>
       <c r="M6">
-        <v>24383.7500810488</v>
+        <v>24425.6377990704</v>
       </c>
       <c r="N6">
         <v>0.194</v>
@@ -1027,31 +1027,31 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>1.433604537244075</v>
+        <v>1.432620438219385</v>
       </c>
       <c r="F7">
-        <v>0.607103281611996</v>
+        <v>0.617241167033028</v>
       </c>
       <c r="G7">
-        <v>2.56164382374705</v>
+        <v>2.536865107656123</v>
       </c>
       <c r="H7">
-        <v>0.09584432329581485</v>
+        <v>0.09664500423129195</v>
       </c>
       <c r="I7">
-        <v>0.057403784364855</v>
+        <v>0.05690907484368378</v>
       </c>
       <c r="J7">
-        <v>0.213382338326494</v>
+        <v>0.209631402779576</v>
       </c>
       <c r="K7">
-        <v>0.388099932615425</v>
+        <v>0.390229825570852</v>
       </c>
       <c r="L7">
-        <v>1794.34354692005</v>
+        <v>1791.01693109292</v>
       </c>
       <c r="M7">
-        <v>23091.7867810321</v>
+        <v>23571.62167466025</v>
       </c>
       <c r="N7">
         <v>0.15</v>
@@ -1077,37 +1077,37 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>1.41321359013919</v>
+        <v>1.41686254652174</v>
       </c>
       <c r="F8">
-        <v>0.5608464742711859</v>
+        <v>0.6001835521510313</v>
       </c>
       <c r="G8">
-        <v>2.358416543142448</v>
+        <v>2.251553617920109</v>
       </c>
       <c r="H8">
-        <v>0.09671380019870809</v>
+        <v>0.0976143196199086</v>
       </c>
       <c r="I8">
-        <v>0.0588383347485048</v>
+        <v>0.06180586796145121</v>
       </c>
       <c r="J8">
-        <v>0.2571935570996194</v>
+        <v>0.2450851575867843</v>
       </c>
       <c r="K8">
-        <v>0.427465698535343</v>
+        <v>0.433134365126817</v>
       </c>
       <c r="L8">
-        <v>1785.875238738125</v>
+        <v>1794.76870347512</v>
       </c>
       <c r="M8">
-        <v>24098.50194021</v>
+        <v>23689.4724238241</v>
       </c>
       <c r="N8">
-        <v>0.126</v>
+        <v>0.101</v>
       </c>
       <c r="O8">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>2023</v>
@@ -1127,37 +1127,37 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>1.42312023570436</v>
+        <v>1.4221721564582</v>
       </c>
       <c r="F9">
-        <v>0.6614800508977066</v>
+        <v>0.5709875488810642</v>
       </c>
       <c r="G9">
-        <v>2.297644291974763</v>
+        <v>2.444339838164967</v>
       </c>
       <c r="H9">
-        <v>0.09756228700640751</v>
+        <v>0.0968764250349024</v>
       </c>
       <c r="I9">
-        <v>0.0615606160615277</v>
+        <v>0.05740740266308921</v>
       </c>
       <c r="J9">
-        <v>0.227529270604775</v>
+        <v>0.2569036105448783</v>
       </c>
       <c r="K9">
-        <v>0.433549132192562</v>
+        <v>0.426162166109578</v>
       </c>
       <c r="L9">
-        <v>1793.72267209929</v>
+        <v>1784.28371222526</v>
       </c>
       <c r="M9">
-        <v>23700.9386785492</v>
+        <v>24181.7959604294</v>
       </c>
       <c r="N9">
-        <v>0.101</v>
+        <v>0.126</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="P9">
         <v>2023</v>
@@ -1177,31 +1177,31 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>1.57363377939101</v>
+        <v>1.562115426696055</v>
       </c>
       <c r="F10">
-        <v>0.551555267481431</v>
+        <v>0.5682001498533449</v>
       </c>
       <c r="G10">
-        <v>2.80725102353407</v>
+        <v>2.631693484500964</v>
       </c>
       <c r="H10">
-        <v>0.0860809933138327</v>
+        <v>0.08654736301081375</v>
       </c>
       <c r="I10">
-        <v>0.0495951078237984</v>
+        <v>0.05225920313396248</v>
       </c>
       <c r="J10">
-        <v>0.267829738933611</v>
+        <v>0.2447670856857318</v>
       </c>
       <c r="K10">
-        <v>0.441458706599035</v>
+        <v>0.4400714903591675</v>
       </c>
       <c r="L10">
-        <v>1826.70712037822</v>
+        <v>1823.74247477741</v>
       </c>
       <c r="M10">
-        <v>22402.8262819572</v>
+        <v>22580.90052802125</v>
       </c>
       <c r="N10">
         <v>0.082</v>
